--- a/forms/trg/Formulir_TRG_hncd-rg.xlsx
+++ b/forms/trg/Formulir_TRG_hncd-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Elly L Sjattar, S.Kp., M.Kes</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -963,7 +967,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1012,7 +1016,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1061,7 +1065,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1155,7 +1159,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1253,7 +1257,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1298,7 +1302,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1343,7 +1347,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1388,7 +1392,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1433,7 +1437,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1474,7 +1478,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1515,7 +1519,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1560,7 +1564,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1650,7 +1654,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1695,7 +1699,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1765,7 +1769,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1794,7 +1798,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1831,7 +1835,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1839,7 +1843,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E26" s="11" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the Holistic Nursing for Chronic Diseases Research Group Advancing holistic, patient-centered care for chronic diseases like diabetes and CKD through research, collaboration, and innovation.</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
@@ -1872,7 +1880,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
